--- a/ig/main/ValueSet-1.2.250.1.213.1.1.5.595.xlsx
+++ b/ig/main/ValueSet-1.2.250.1.213.1.1.5.595.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="66">
   <si>
     <t>Property</t>
   </si>
@@ -74,19 +74,7 @@
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>ANS (https://esante.gouv.fr)</t>
-  </si>
-  <si>
-    <t>Jurisdiction</t>
-  </si>
-  <si>
-    <t>France</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Description</t>
@@ -361,7 +349,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -453,43 +441,27 @@
         <v>19</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>22</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>9</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="B14" s="2"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B15" s="2"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>27</v>
+        <v>22</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -508,34 +480,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -554,82 +526,82 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -648,50 +620,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -710,34 +682,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -756,58 +728,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -826,42 +798,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/ValueSet-1.2.250.1.213.1.1.5.595.xlsx
+++ b/ig/main/ValueSet-1.2.250.1.213.1.1.5.595.xlsx
@@ -10,15 +10,12 @@
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
     <sheet name="Include #2" r:id="rId6" sheetId="4"/>
-    <sheet name="Include #3" r:id="rId7" sheetId="5"/>
-    <sheet name="Include #4" r:id="rId8" sheetId="6"/>
-    <sheet name="Include #5" r:id="rId9" sheetId="7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="66">
   <si>
     <t>Property</t>
   </si>
@@ -68,13 +65,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-19T01:00:00+02:00</t>
+    <t>2024-07-19T00:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
+    <t>Agence du Numérique en Santé(ANS) -2 - 10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Description</t>
@@ -95,127 +92,127 @@
     <t>Concept</t>
   </si>
   <si>
+    <t>C15313</t>
+  </si>
+  <si>
+    <t>radiothérapie</t>
+  </si>
+  <si>
+    <t>C15195</t>
+  </si>
+  <si>
+    <t>curiethérapie</t>
+  </si>
+  <si>
+    <t>C15632</t>
+  </si>
+  <si>
+    <t>chimiothérapie</t>
+  </si>
+  <si>
+    <t>C93352</t>
+  </si>
+  <si>
+    <t>thérapie ciblée</t>
+  </si>
+  <si>
+    <t>C547</t>
+  </si>
+  <si>
+    <t>Hormonothérapie</t>
+  </si>
+  <si>
+    <t>C15262</t>
+  </si>
+  <si>
+    <t>immunothérapie</t>
+  </si>
+  <si>
+    <t>C63334</t>
+  </si>
+  <si>
+    <t>Radiologie interventionnelle</t>
+  </si>
+  <si>
+    <t>C157891</t>
+  </si>
+  <si>
+    <t>endoscopie interventionnelle</t>
+  </si>
+  <si>
+    <t>C15747</t>
+  </si>
+  <si>
+    <t>soins de support</t>
+  </si>
+  <si>
+    <t>C15252</t>
+  </si>
+  <si>
+    <t>soins palliatifs</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/terminologie-ncit</t>
+  </si>
+  <si>
+    <t>MED-556</t>
+  </si>
+  <si>
+    <t>Fenêtre thérapeutique</t>
+  </si>
+  <si>
+    <t>MED-226</t>
+  </si>
+  <si>
+    <t>Surveillance seule</t>
+  </si>
+  <si>
+    <t>MED-227</t>
+  </si>
+  <si>
+    <t>Surveillance active</t>
+  </si>
+  <si>
+    <t>MED-232</t>
+  </si>
+  <si>
+    <t>Irathérapie</t>
+  </si>
+  <si>
+    <t>MED-126</t>
+  </si>
+  <si>
+    <t>Allogreffe / Autogreffe</t>
+  </si>
+  <si>
+    <t>GEN-092.03.01</t>
+  </si>
+  <si>
+    <t>Autre(s) traitement(s)</t>
+  </si>
+  <si>
+    <t>GEN-092.03.02</t>
+  </si>
+  <si>
+    <t>Autre(s) traitement(s) médicamenteux spécifique(s)</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/1.2.250.1.213.1.1.4.322</t>
+  </si>
+  <si>
     <t>387713003</t>
   </si>
   <si>
     <t>intervention chirurgicale</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>System URI</t>
-  </si>
-  <si>
-    <t>urn:oid:2.16.840.1.113883.6.96</t>
-  </si>
-  <si>
-    <t>C15313</t>
-  </si>
-  <si>
-    <t>radiothérapie</t>
-  </si>
-  <si>
-    <t>C15195</t>
-  </si>
-  <si>
-    <t>curiethérapie</t>
-  </si>
-  <si>
-    <t>C15632</t>
-  </si>
-  <si>
-    <t>chimiothérapie</t>
-  </si>
-  <si>
-    <t>C93352</t>
-  </si>
-  <si>
-    <t>thérapie ciblée</t>
-  </si>
-  <si>
-    <t>C547</t>
-  </si>
-  <si>
-    <t>Hormonothérapie</t>
-  </si>
-  <si>
-    <t>C15262</t>
-  </si>
-  <si>
-    <t>immunothérapie</t>
-  </si>
-  <si>
-    <t>C63334</t>
-  </si>
-  <si>
-    <t>Radiologie interventionnelle</t>
-  </si>
-  <si>
-    <t>urn:oid:2.16.840.1.113883.3.26.1.1</t>
-  </si>
-  <si>
-    <t>MED-556</t>
-  </si>
-  <si>
-    <t>Fenêtre thérapeutique</t>
-  </si>
-  <si>
-    <t>MED-226</t>
-  </si>
-  <si>
-    <t>Surveillance seule</t>
-  </si>
-  <si>
-    <t>MED-227</t>
-  </si>
-  <si>
-    <t>Surveillance active</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/1.2.250.1.213.1.1.4.322</t>
-  </si>
-  <si>
-    <t>C157891</t>
-  </si>
-  <si>
-    <t>endoscopie interventionnelle</t>
-  </si>
-  <si>
-    <t>MED-232</t>
-  </si>
-  <si>
-    <t>Irathérapie</t>
-  </si>
-  <si>
-    <t>MED-126</t>
-  </si>
-  <si>
-    <t>Allogreffe / Autogreffe</t>
-  </si>
-  <si>
-    <t>GEN-092.03.01</t>
-  </si>
-  <si>
-    <t>Autre(s) traitement(s)</t>
-  </si>
-  <si>
-    <t>GEN-092.03.02</t>
-  </si>
-  <si>
-    <t>Autre(s) traitement(s) médicamenteux spécifique(s)</t>
-  </si>
-  <si>
-    <t>C15747</t>
-  </si>
-  <si>
-    <t>soins de support</t>
-  </si>
-  <si>
-    <t>C15252</t>
-  </si>
-  <si>
-    <t>soins palliatifs</t>
+    <t>http://snomed.info/sct</t>
   </si>
 </sst>
 </file>
@@ -471,7 +468,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -499,15 +496,87 @@
         <v>27</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -534,74 +603,74 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>31</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>33</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>35</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>37</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>41</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>43</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>27</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>44</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -610,68 +679,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>24</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>51</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -690,150 +697,26 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>53</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>27</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>44</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>24</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>51</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>24</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="B3" t="s" s="2">
         <v>65</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/ValueSet-1.2.250.1.213.1.1.5.595.xlsx
+++ b/ig/main/ValueSet-1.2.250.1.213.1.1.5.595.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="68">
   <si>
     <t>Property</t>
   </si>
@@ -72,6 +72,12 @@
   </si>
   <si>
     <t>Agence du Numérique en Santé(ANS) -2 - 10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>
@@ -346,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -438,27 +444,35 @@
         <v>19</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="B12" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>9</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="B14" t="s" s="2">
         <v>23</v>
+      </c>
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -477,106 +491,106 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -595,82 +609,82 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -689,34 +703,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
